--- a/final_task/employees.xlsx
+++ b/final_task/employees.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anaer\OneDrive\Desktop\inform\final_task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BD2A7DE-7B90-4473-9A1A-886E3798C4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD43910-C8F7-4D1E-A5D9-A4E2A9D1D652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employees" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="61">
   <si>
     <t>full_name</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>quest_text</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
@@ -266,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -276,6 +279,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -498,7 +502,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -506,7 +510,7 @@
     <col min="3" max="3" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,8 +520,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -527,8 +534,11 @@
       <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="5">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -538,8 +548,11 @@
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="5">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -549,8 +562,11 @@
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="5">
+        <v>3333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -560,8 +576,11 @@
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="5">
+        <v>4444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -571,8 +590,11 @@
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="5">
+        <v>5555</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -582,8 +604,11 @@
       <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="5">
+        <v>6666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -593,8 +618,11 @@
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="5">
+        <v>7777</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -604,8 +632,11 @@
       <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="5">
+        <v>8888</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -615,8 +646,11 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="5">
+        <v>9999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
@@ -626,8 +660,11 @@
       <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="5">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -637,8 +674,11 @@
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="5">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
@@ -648,8 +688,11 @@
       <c r="C13" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="5">
+        <v>5678</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -659,8 +702,11 @@
       <c r="C14" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="5">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
@@ -670,8 +716,11 @@
       <c r="C15" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="5">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>36</v>
       </c>
@@ -681,8 +730,11 @@
       <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="5">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
@@ -692,8 +744,11 @@
       <c r="C17" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="5">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>40</v>
       </c>
@@ -703,8 +758,11 @@
       <c r="C18" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="5">
+        <v>7535</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -714,8 +772,11 @@
       <c r="C19" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="5">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
@@ -725,8 +786,11 @@
       <c r="C20" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="5">
+        <v>5467</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -735,6 +799,9 @@
       </c>
       <c r="C21" s="1" t="s">
         <v>46</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4324</v>
       </c>
     </row>
   </sheetData>
